--- a/request_forms/024_sku_deactivation_approval_request_form--request_forms.xlsx
+++ b/request_forms/024_sku_deactivation_approval_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,35 +612,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>reason_for_deactivation</t>
+          <t>sku_id</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reason for Deactivation</t>
+          <t>SKU ID</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>deactivation_date</t>
+          <t>additional_notes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Deactivation Date</t>
+          <t>Additional Notes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>deactivation_time</t>
+          <t>sales_representative</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Deactivation Time</t>
+          <t>Sales Representative</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,16 +681,85 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sku_id</t>
+          <t>reason_for_deactivation_if_no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SKU ID</t>
+          <t>Reason for Deactivation (if no)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>deactivation_time_if_no</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Deactivation Time (if no)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>deactivation_date_if_no</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Deactivation Date (if no)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sku_id_if_no</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SKU ID (if no)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -711,7 +780,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -740,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -757,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
